--- a/data/extracted/inventory-receipts/REP CONTENEDOR PERUANA 250GRMS.XLSX
+++ b/data/extracted/inventory-receipts/REP CONTENEDOR PERUANA 250GRMS.XLSX
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD13BF0-108B-445C-B36B-7D93C6B51FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9135"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -908,7 +921,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -949,12 +962,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1234,50 +1246,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L143"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1315,12 +1327,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1358,7 +1370,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -1396,7 +1408,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,7 +1446,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1472,7 +1484,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1510,7 +1522,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1548,7 +1560,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1586,7 +1598,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -1624,7 +1636,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -1662,7 +1674,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1700,7 +1712,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -1738,7 +1750,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -1776,7 +1788,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -1814,7 +1826,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1852,7 +1864,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -1890,7 +1902,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -1928,7 +1940,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -1966,7 +1978,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2004,7 +2016,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2042,7 +2054,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -2080,7 +2092,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -2118,7 +2130,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -2156,7 +2168,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -2194,7 +2206,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -2232,7 +2244,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -2270,7 +2282,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -2308,7 +2320,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -2346,7 +2358,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -2384,7 +2396,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -2422,7 +2434,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -2460,7 +2472,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -2498,7 +2510,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -2536,7 +2548,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -2574,7 +2586,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -2612,7 +2624,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -2650,7 +2662,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -2688,7 +2700,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -2726,7 +2738,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -2764,7 +2776,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -2802,7 +2814,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -2840,7 +2852,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -2878,7 +2890,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -2916,7 +2928,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -2954,7 +2966,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -2992,7 +3004,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -3030,7 +3042,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -3068,7 +3080,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -3106,7 +3118,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -3144,7 +3156,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -3182,7 +3194,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -3220,7 +3232,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -3258,7 +3270,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -3296,7 +3308,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -3334,7 +3346,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -3372,7 +3384,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -3410,7 +3422,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -3448,7 +3460,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -3486,7 +3498,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3524,7 +3536,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -3562,7 +3574,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>19</v>
       </c>
@@ -3600,7 +3612,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -3638,7 +3650,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -3676,7 +3688,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -3714,7 +3726,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -3752,7 +3764,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -3790,7 +3802,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>19</v>
       </c>
@@ -3828,7 +3840,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -3866,7 +3878,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -3904,7 +3916,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -3942,7 +3954,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -3980,7 +3992,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -4018,7 +4030,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -4056,7 +4068,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -4094,7 +4106,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -4132,7 +4144,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -4170,7 +4182,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -4208,7 +4220,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -4246,7 +4258,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
@@ -4284,7 +4296,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -4322,7 +4334,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -4360,7 +4372,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -4398,7 +4410,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -4436,7 +4448,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -4474,7 +4486,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -4512,7 +4524,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -4550,7 +4562,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -4588,7 +4600,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>19</v>
       </c>
@@ -4626,7 +4638,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>19</v>
       </c>
@@ -4664,7 +4676,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
@@ -4702,7 +4714,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -4740,7 +4752,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -4778,7 +4790,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>19</v>
       </c>
@@ -4816,7 +4828,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -4854,7 +4866,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -4892,7 +4904,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>19</v>
       </c>
@@ -4930,7 +4942,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>19</v>
       </c>
@@ -4968,7 +4980,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -5006,7 +5018,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -5044,7 +5056,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -5082,7 +5094,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -5120,7 +5132,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -5158,7 +5170,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -5196,7 +5208,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -5234,7 +5246,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -5272,7 +5284,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -5310,7 +5322,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -5348,7 +5360,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>19</v>
       </c>
@@ -5386,7 +5398,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>19</v>
       </c>
@@ -5424,7 +5436,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -5462,7 +5474,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>19</v>
       </c>
@@ -5500,7 +5512,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -5538,7 +5550,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
@@ -5576,7 +5588,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -5614,7 +5626,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -5652,7 +5664,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>19</v>
       </c>
@@ -5690,7 +5702,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>19</v>
       </c>
@@ -5728,7 +5740,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>19</v>
       </c>
@@ -5766,7 +5778,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>19</v>
       </c>
@@ -5804,7 +5816,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>19</v>
       </c>
@@ -5842,7 +5854,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>19</v>
       </c>
@@ -5880,7 +5892,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>19</v>
       </c>
@@ -5918,7 +5930,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>19</v>
       </c>
@@ -5956,7 +5968,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>19</v>
       </c>
@@ -5994,7 +6006,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>19</v>
       </c>
@@ -6032,7 +6044,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>19</v>
       </c>
@@ -6070,7 +6082,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>19</v>
       </c>
@@ -6108,7 +6120,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>19</v>
       </c>
@@ -6146,7 +6158,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
@@ -6184,7 +6196,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>19</v>
       </c>
@@ -6222,7 +6234,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>19</v>
       </c>
@@ -6260,7 +6272,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>19</v>
       </c>
@@ -6298,7 +6310,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F138" s="1" t="s">
         <v>287</v>
       </c>
@@ -6318,7 +6330,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F139" s="1" t="s">
         <v>125</v>
       </c>
@@ -6335,7 +6347,7 @@
         <v>2367.599999999994</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F140" s="1" t="s">
         <v>287</v>
       </c>
@@ -6355,7 +6367,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>289</v>
       </c>
@@ -6393,7 +6405,7 @@
         <v>146.30000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F143" s="1" t="s">
         <v>287</v>
       </c>
@@ -6417,4 +6429,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8EBB164-D656-4CE4-8794-A62DC948212C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47502</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>